--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487596_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487596_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>B. FERNANDEZ SHEPHARD</t>
+          <t>E. DUQUE NEGRÍN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3686</v>
+        <v>4.3318</v>
       </c>
       <c r="E2" t="n">
-        <v>3.1092</v>
+        <v>2.4892</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2593</v>
+        <v>1.8426</v>
       </c>
       <c r="G2" t="n">
-        <v>-1.3989</v>
+        <v>2.5207</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4012</v>
+        <v>2.4634</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.9977</v>
+        <v>0.0573</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.5407999999999999</v>
+        <v>2.4728</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0453</v>
+        <v>1.8537</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5861</v>
+        <v>0.619</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8581</v>
+        <v>0.0479</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4466</v>
+        <v>0.6096</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4115</v>
+        <v>-0.5617</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3582</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.194</v>
+        <v>-2.3284</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5523</v>
+        <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2436</v>
+        <v>0.8395</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3963</v>
+        <v>0.8389</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1527</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1657</v>
+        <v>1.5537</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4477</v>
+        <v>1.506</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2821</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. DUQUE NEGRÍN</t>
+          <t>J. GALLETTO LAMELA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2312</v>
+        <v>2.8345</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6884</v>
+        <v>2.8796</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5428</v>
+        <v>-0.0451</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5207</v>
+        <v>0.4376</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4634</v>
+        <v>0.0256</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0573</v>
+        <v>0.4121</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4728</v>
+        <v>1.9136</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8537</v>
+        <v>1.2235</v>
       </c>
       <c r="L3" t="n">
-        <v>0.619</v>
+        <v>0.6901</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0479</v>
+        <v>-1.476</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6096</v>
+        <v>-1.1979</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5617</v>
+        <v>-0.2781</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.5821</v>
+        <v>1.7463</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.3284</v>
+        <v>-0.194</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7463</v>
+        <v>1.9403</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2611</v>
+        <v>1.0282</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0381</v>
+        <v>0.3137</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2992</v>
+        <v>0.7145</v>
       </c>
       <c r="V3" t="n">
-        <v>1.5537</v>
+        <v>-0.3776</v>
       </c>
       <c r="W3" t="n">
-        <v>1.506</v>
+        <v>0.8462</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0478</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GALLETTO LAMELA</t>
+          <t>B. FERNANDEZ SHEPHARD</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3646</v>
+        <v>2.6406</v>
       </c>
       <c r="E4" t="n">
-        <v>2.5187</v>
+        <v>2.4085</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1541</v>
+        <v>0.2321</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4376</v>
+        <v>-1.3989</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0256</v>
+        <v>-0.4012</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4121</v>
+        <v>-0.9977</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9136</v>
+        <v>-0.5407999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2235</v>
+        <v>0.0453</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6901</v>
+        <v>-0.5861</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.476</v>
+        <v>-0.8581</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1979</v>
+        <v>-0.4466</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2781</v>
+        <v>-0.4115</v>
       </c>
       <c r="P4" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.194</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9403</v>
+        <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5583</v>
+        <v>0.5155999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0471</v>
+        <v>0.6956</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6054</v>
+        <v>-0.18</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3776</v>
+        <v>2.1657</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8462</v>
+        <v>2.4477</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. NIMAGA</t>
+          <t>L. GIFREU LLARCH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7996</v>
+        <v>1.1086</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1127</v>
+        <v>-0.4932</v>
       </c>
       <c r="F5" t="n">
-        <v>1.687</v>
+        <v>1.6018</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.0829</v>
+        <v>1.9716</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9211</v>
+        <v>0.8527</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1619</v>
+        <v>1.1189</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2077</v>
+        <v>2.5185</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3295</v>
+        <v>0.7044</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1218</v>
+        <v>1.8141</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8752</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5916</v>
+        <v>0.1483</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2836</v>
+        <v>-0.6952</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.1344</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.0747</v>
+        <v>-3.8806</v>
       </c>
       <c r="R5" t="n">
         <v>1.9403</v>
       </c>
       <c r="S5" t="n">
-        <v>4.0751</v>
+        <v>0.0878</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8891</v>
+        <v>0.5868</v>
       </c>
       <c r="U5" t="n">
-        <v>1.186</v>
+        <v>-0.4991</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9418</v>
+        <v>0.9896</v>
       </c>
       <c r="W5" t="n">
-        <v>1.506</v>
+        <v>0.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5642</v>
+        <v>0.7075</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. GIFREU LLARCH</t>
+          <t>K. RIVEROL DE LAS CASAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2811</v>
+        <v>0.6218</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9937</v>
+        <v>1.2989</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2748</v>
+        <v>-0.6771</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9716</v>
+        <v>0.4406</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8527</v>
+        <v>-0.075</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1189</v>
+        <v>0.5155</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5185</v>
+        <v>2.2556</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7044</v>
+        <v>1.0504</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8141</v>
+        <v>1.2052</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-1.815</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1483</v>
+        <v>-1.1254</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6952</v>
+        <v>-0.6896</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7398</v>
+        <v>0.1335</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0863</v>
+        <v>0.0134</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8260999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9896</v>
+        <v>0.0478</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7075</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. KHIVRENKO</t>
+          <t>A. SISTAC RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1397</v>
+        <v>0.0696</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2902</v>
+        <v>-3.9069</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4298</v>
+        <v>3.9765</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.4098</v>
+        <v>0.7844</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.5555</v>
+        <v>-1.1353</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1457</v>
+        <v>1.9197</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.0075</v>
+        <v>0.4644</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1699</v>
+        <v>-0.7991</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1624</v>
+        <v>1.2635</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4023</v>
+        <v>0.32</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3856</v>
+        <v>-0.3362</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0167</v>
+        <v>0.6562</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3284</v>
+        <v>-4.2687</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1642</v>
+        <v>2.3284</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8196</v>
+        <v>1.5553</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4816</v>
+        <v>0.5571</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3381</v>
+        <v>0.9982</v>
       </c>
       <c r="V7" t="n">
-        <v>0.894</v>
+        <v>-0.3299</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5642</v>
+        <v>-0.6597</v>
       </c>
       <c r="X7" t="n">
         <v>0.3299</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. RIVEROL DE LAS CASAS</t>
+          <t>M. NIMAGA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0518</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8379</v>
+        <v>-1.2887</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7861</v>
+        <v>1.1964</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4406</v>
+        <v>-1.0829</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.075</v>
+        <v>-0.9211</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5155</v>
+        <v>-0.1619</v>
       </c>
       <c r="J8" t="n">
-        <v>2.2556</v>
+        <v>-0.2077</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0504</v>
+        <v>-0.3295</v>
       </c>
       <c r="L8" t="n">
-        <v>1.2052</v>
+        <v>0.1218</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.815</v>
+        <v>-0.8752</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.1254</v>
+        <v>-0.5916</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6896</v>
+        <v>-0.2836</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-2.1344</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>-4.0747</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4365</v>
+        <v>2.1831</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4475</v>
+        <v>1.4877</v>
       </c>
       <c r="U8" t="n">
-        <v>0.011</v>
+        <v>0.6954</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0478</v>
+        <v>0.9418</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0478</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SISTAC RODRIGUEZ</t>
+          <t>M. KHIVRENKO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5281</v>
+        <v>-0.3459</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6682</v>
+        <v>-1.8302</v>
       </c>
       <c r="F9" t="n">
-        <v>4.14</v>
+        <v>1.4843</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7844</v>
+        <v>-1.4098</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1353</v>
+        <v>-1.5555</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9197</v>
+        <v>0.1457</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4644</v>
+        <v>-1.0075</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7991</v>
+        <v>-1.1699</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2635</v>
+        <v>0.1624</v>
       </c>
       <c r="M9" t="n">
-        <v>0.32</v>
+        <v>-0.4023</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3362</v>
+        <v>-0.3856</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6562</v>
+        <v>-0.0167</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.2687</v>
+        <v>-2.3284</v>
       </c>
       <c r="R9" t="n">
-        <v>2.3284</v>
+        <v>1.1642</v>
       </c>
       <c r="S9" t="n">
-        <v>0.9576</v>
+        <v>1.3341</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2042</v>
+        <v>0.9415</v>
       </c>
       <c r="U9" t="n">
-        <v>1.1618</v>
+        <v>0.3926</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3299</v>
+        <v>0.894</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6597</v>
+        <v>0.5642</v>
       </c>
       <c r="X9" t="n">
         <v>0.3299</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.391</v>
+        <v>-1.7754</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.191</v>
+        <v>-4.6299</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8</v>
+        <v>2.8545</v>
       </c>
       <c r="G10" t="n">
         <v>-3.8126</v>
@@ -1234,13 +1234,13 @@
         <v>2.1344</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1216</v>
+        <v>0.7371</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.35</v>
+        <v>0.2111</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4715</v>
+        <v>0.526</v>
       </c>
       <c r="V10" t="n">
         <v>0.3299</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.0119</v>
+        <v>-3.785</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1672</v>
+        <v>-1.6677</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.8448</v>
+        <v>-2.1173</v>
       </c>
       <c r="G11" t="n">
         <v>-3.1519</v>
@@ -1312,13 +1312,13 @@
         <v>0.7761</v>
       </c>
       <c r="S11" t="n">
-        <v>1.1519</v>
+        <v>0.3788</v>
       </c>
       <c r="T11" t="n">
-        <v>1.0565</v>
+        <v>0.556</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0954</v>
+        <v>-0.1772</v>
       </c>
       <c r="V11" t="n">
         <v>-1.788</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.305599999999999</v>
+        <v>5.6083</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0434</v>
+        <v>-4.740399999999999</v>
       </c>
       <c r="F12" t="n">
         <v>10.3487</v>
@@ -1369,7 +1369,7 @@
         <v>-1.178</v>
       </c>
       <c r="L12" t="n">
-        <v>2.8643</v>
+        <v>2.864300000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-6.3876</v>
@@ -1390,13 +1390,13 @@
         <v>16.4928</v>
       </c>
       <c r="S12" t="n">
-        <v>8.4903</v>
+        <v>8.792999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>5.899100000000001</v>
+        <v>6.2018</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5912</v>
+        <v>2.591</v>
       </c>
       <c r="V12" t="n">
         <v>4.427</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>G. HIERRO ABAD</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.6338</v>
+        <v>2.9685</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7513</v>
+        <v>2.5857</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8825</v>
+        <v>0.3828</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6623</v>
+        <v>2.0157</v>
       </c>
       <c r="H13" t="n">
-        <v>5.0948</v>
+        <v>-0.786</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.4326</v>
+        <v>2.8017</v>
       </c>
       <c r="J13" t="n">
-        <v>4.2322</v>
+        <v>3.3865</v>
       </c>
       <c r="K13" t="n">
-        <v>4.8361</v>
+        <v>0.1565</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6039</v>
+        <v>3.23</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.57</v>
+        <v>-1.3708</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2587</v>
+        <v>-0.9425</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8286</v>
+        <v>-0.4282</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.3881</v>
+        <v>-1.9403</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3284</v>
+        <v>2.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9897</v>
+        <v>-0.8636</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7257</v>
+        <v>-0.2709</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.264</v>
+        <v>-0.5927</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.9791</v>
+        <v>0.8462</v>
       </c>
       <c r="W13" t="n">
-        <v>-1.3672</v>
+        <v>1.4104</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6119</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. PRATS PEINADO</t>
+          <t>E. ECHEVERRIA MATEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.161</v>
+        <v>2.9508</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9054</v>
+        <v>2.2065</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2556</v>
+        <v>0.7443</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.573</v>
+        <v>5.4587</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3411</v>
+        <v>2.9478</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2319</v>
+        <v>2.5109</v>
       </c>
       <c r="J14" t="n">
-        <v>0.123</v>
+        <v>4.8275</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0824</v>
+        <v>2.4222</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0406</v>
+        <v>2.4053</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.696</v>
+        <v>0.6312</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4235</v>
+        <v>0.5256</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.2725</v>
+        <v>0.1056</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9702</v>
+        <v>3.1045</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5399</v>
+        <v>-1.6706</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5585</v>
+        <v>-0.7493</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0186</v>
+        <v>-0.9213</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2239</v>
+        <v>-2.7776</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2239</v>
+        <v>-0.7075</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.0701</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. HIERRO ABAD</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1527</v>
+        <v>2.7043</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3855</v>
+        <v>1.7513</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2328</v>
+        <v>0.953</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0157</v>
+        <v>3.6623</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.786</v>
+        <v>5.0948</v>
       </c>
       <c r="I15" t="n">
-        <v>2.8017</v>
+        <v>-1.4326</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3865</v>
+        <v>4.2322</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1565</v>
+        <v>4.8361</v>
       </c>
       <c r="L15" t="n">
-        <v>3.23</v>
+        <v>-0.6039</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3708</v>
+        <v>-0.57</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9425</v>
+        <v>0.2587</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4282</v>
+        <v>-0.8286</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9702</v>
+        <v>1.9403</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9403</v>
+        <v>-0.3881</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9105</v>
+        <v>2.3284</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6794</v>
+        <v>-0.9191</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4711</v>
+        <v>-0.7257</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2084</v>
+        <v>-0.1934</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8462</v>
+        <v>-1.9791</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4104</v>
+        <v>-1.3672</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5642</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. ECHEVERRIA MATEO</t>
+          <t>J. PRATS PEINADO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7412</v>
+        <v>1.7789</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8061</v>
+        <v>1.6051</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0649</v>
+        <v>0.1738</v>
       </c>
       <c r="G16" t="n">
-        <v>5.4587</v>
+        <v>-0.573</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9478</v>
+        <v>-0.3411</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5109</v>
+        <v>-0.2319</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8275</v>
+        <v>0.123</v>
       </c>
       <c r="K16" t="n">
-        <v>2.4222</v>
+        <v>0.0824</v>
       </c>
       <c r="L16" t="n">
-        <v>2.4053</v>
+        <v>0.0406</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6312</v>
+        <v>-0.696</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5256</v>
+        <v>-0.4235</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1056</v>
+        <v>-0.2725</v>
       </c>
       <c r="P16" t="n">
-        <v>1.9403</v>
+        <v>0.9702</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1045</v>
+        <v>0.9702</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.8802</v>
+        <v>0.1579</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1497</v>
+        <v>0.2582</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.7305</v>
+        <v>-0.1004</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.7776</v>
+        <v>1.2239</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.7075</v>
+        <v>1.2239</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.0701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9618</v>
+        <v>1.0892</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0341</v>
+        <v>1.1342</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0722</v>
+        <v>-0.045</v>
       </c>
       <c r="G17" t="n">
         <v>0.3341</v>
@@ -1780,13 +1780,13 @@
         <v>0.3881</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0424</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.173</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1153</v>
+        <v>-0.08799999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>0.2821</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5377</v>
+        <v>-0.2919</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5275</v>
+        <v>-2.2272</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9898</v>
+        <v>1.9353</v>
       </c>
       <c r="G18" t="n">
         <v>0.3723</v>
@@ -1858,13 +1858,13 @@
         <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1041</v>
+        <v>-0.8583</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9085</v>
+        <v>-0.6082</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1956</v>
+        <v>-0.2501</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MARTIN LLUNA</t>
+          <t>V. FERNANDEZ MORAN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5765</v>
+        <v>-0.3465</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4668</v>
+        <v>-1.6939</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8904</v>
+        <v>1.3474</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1713</v>
+        <v>-0.3863</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.6362</v>
+        <v>-1.0191</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4649</v>
+        <v>0.6328</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.1762</v>
+        <v>0.5841</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.2574</v>
+        <v>-0.2101</v>
       </c>
       <c r="L19" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.7942</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0049</v>
+        <v>-0.9704</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6212</v>
+        <v>-0.8091</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3837</v>
+        <v>-0.1613</v>
       </c>
       <c r="P19" t="n">
         <v>0.9702</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="R19" t="n">
-        <v>2.1344</v>
+        <v>2.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1889</v>
+        <v>-0.9304</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5915</v>
+        <v>-0.3376</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4026</v>
+        <v>-0.5927</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.8462</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ MORAN</t>
+          <t>D. MARTIN LLUNA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.09</v>
+        <v>-1.42</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.4947</v>
+        <v>-2.7681</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4047</v>
+        <v>1.3481</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3863</v>
+        <v>-1.1713</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0191</v>
+        <v>-1.6362</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6328</v>
+        <v>0.4649</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5841</v>
+        <v>-2.1762</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2101</v>
+        <v>-2.2574</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7942</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9704</v>
+        <v>1.0049</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8091</v>
+        <v>0.6212</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1613</v>
+        <v>0.3837</v>
       </c>
       <c r="P20" t="n">
         <v>0.9702</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="R20" t="n">
-        <v>2.9105</v>
+        <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6738</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1384</v>
+        <v>0.2902</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.5354</v>
+        <v>-0.9449</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7507</v>
+        <v>-3.1389</v>
       </c>
       <c r="E21" t="n">
-        <v>0.377</v>
+        <v>-0.2236</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1277</v>
+        <v>-2.9153</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9056</v>
@@ -2092,13 +2092,13 @@
         <v>0.9702</v>
       </c>
       <c r="S21" t="n">
-        <v>0.825</v>
+        <v>0.4368</v>
       </c>
       <c r="T21" t="n">
-        <v>0.729</v>
+        <v>0.1284</v>
       </c>
       <c r="U21" t="n">
-        <v>0.096</v>
+        <v>0.3084</v>
       </c>
       <c r="V21" t="n">
         <v>-1.506</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9023</v>
+        <v>-3.8468</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.843299999999999</v>
+        <v>-8.242699999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>4.941</v>
+        <v>4.3959</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4501</v>
@@ -2170,13 +2170,13 @@
         <v>1.9403</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7537</v>
+        <v>-0.6982</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2719</v>
+        <v>-0.6713</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5182</v>
+        <v>-0.0269</v>
       </c>
       <c r="V22" t="n">
         <v>0.6597</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0988</v>
+        <v>-5.0838</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2757</v>
+        <v>-4.4759</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.6078</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6556</v>
@@ -2248,13 +2248,13 @@
         <v>0.194</v>
       </c>
       <c r="S23" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1222</v>
+        <v>-0.078</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0431</v>
+        <v>0.1722</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6119</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.305499999999999</v>
+        <v>-2.636200000000001</v>
       </c>
       <c r="E24" t="n">
         <v>-10.3486</v>
       </c>
       <c r="F24" t="n">
-        <v>5.043299999999999</v>
+        <v>7.712499999999999</v>
       </c>
       <c r="G24" t="n">
         <v>4.701200000000001</v>
@@ -2326,13 +2326,13 @@
         <v>19.4034</v>
       </c>
       <c r="S24" t="n">
-        <v>-8.490299999999998</v>
+        <v>-5.821000000000001</v>
       </c>
       <c r="T24" t="n">
         <v>-2.5912</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.899299999999999</v>
+        <v>-3.2298</v>
       </c>
       <c r="V24" t="n">
         <v>-4.426900000000001</v>
